--- a/02_DIA_inicio_2026_analisis_assets/rbd_9740_escuela-basica-republica-de-las-filipinas_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9740_escuela-basica-republica-de-las-filipinas_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0166B3AC-9D37-4934-BD6D-D65042935E0B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F170D5-A009-48DB-A3D2-DE38F31D1259}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D29F7D63-8BB6-49D8-AC5B-8CABF570FF7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{992FA3D0-7BB1-46EF-AE5F-D43336BD017D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D4188A0-3302-48E2-A800-673A82BEE66A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2837AFCD-7E25-4EC7-A7E8-FFD01BC87096}"/>
 </file>